--- a/Example_scripts/Input example - from pressure grid.xlsx
+++ b/Example_scripts/Input example - from pressure grid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365tno-my.sharepoint.com/personal/bart_davids_tno_nl/Documents/Documents/PySub/Example_scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{70DE4E5C-224B-4531-87B6-7E834178536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{718B725E-89D7-4E05-8C04-06E72F70DE93}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{70DE4E5C-224B-4531-87B6-7E834178536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E493A0E1-EEB8-4BDC-B2AC-F937A983C0B7}"/>
   <bookViews>
-    <workbookView xWindow="31830" yWindow="4665" windowWidth="28800" windowHeight="15435" activeTab="2" xr2:uid="{555B1425-0405-477B-A81F-DC1674E6CB4A}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{555B1425-0405-477B-A81F-DC1674E6CB4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model parameters" sheetId="1" r:id="rId1"/>
@@ -128,9 +128,6 @@
     <t>b</t>
   </si>
   <si>
-    <t>Reference stress rate (Pa/year)</t>
-  </si>
-  <si>
     <t>Lower error (m)</t>
   </si>
   <si>
@@ -174,6 +171,9 @@
   </si>
   <si>
     <t>Model from grid\Een_thickness.tif</t>
+  </si>
+  <si>
+    <t>Reference stress rate (bar/year)</t>
   </si>
 </sst>
 </file>
@@ -535,18 +535,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B04BB3-B26D-4DD4-818B-00CE2A287B6F}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -563,13 +563,13 @@
         <v>16</v>
       </c>
       <c r="F1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="G1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -618,20 +618,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A316F1A6-ED4E-4962-9A52-869AB762729B}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="110.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.88671875" customWidth="1"/>
+    <col min="5" max="6" width="18.33203125" customWidth="1"/>
+    <col min="7" max="7" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -642,7 +642,7 @@
         <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
@@ -651,19 +651,19 @@
         <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I1" t="s">
         <v>19</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
         <v>27</v>
@@ -672,12 +672,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>6000</v>
@@ -689,7 +689,7 @@
         <v>3000</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G2" s="1">
         <f>0.000012</f>
@@ -716,12 +716,12 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>5000</v>
@@ -733,7 +733,7 @@
         <v>2500</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="1">
         <f t="shared" ref="G3:G4" si="0">0.000012</f>
@@ -760,12 +760,12 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4">
         <v>6500</v>
@@ -777,7 +777,7 @@
         <v>2250</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" s="1">
         <f t="shared" si="0"/>
@@ -817,13 +817,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7091822E-7203-4A87-A3C6-3CE673FC987F}">
   <dimension ref="A1:V4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -891,7 +891,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -968,7 +968,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1131,9 +1131,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49B3CA5E-794D-445C-AECE-934CB5762146}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>567600</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1174,15 +1174,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A82A3235-637C-4DE6-ADD9-2F88DF624BFC}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>25</v>
       </c>
@@ -1196,16 +1196,16 @@
         <v>22</v>
       </c>
       <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -1452,9 +1452,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8EFCC63-8018-45AD-AA9D-4C0BC3366A2B}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>

--- a/Example_scripts/Input example - from pressure grid.xlsx
+++ b/Example_scripts/Input example - from pressure grid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://365tno-my.sharepoint.com/personal/bart_davids_tno_nl/Documents/Documents/PySub/Example_scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{70DE4E5C-224B-4531-87B6-7E834178536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E493A0E1-EEB8-4BDC-B2AC-F937A983C0B7}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{70DE4E5C-224B-4531-87B6-7E834178536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D79C1838-0141-49DC-95AE-FA2E50405423}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{555B1425-0405-477B-A81F-DC1674E6CB4A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{555B1425-0405-477B-A81F-DC1674E6CB4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Model parameters" sheetId="1" r:id="rId1"/>
@@ -215,10 +215,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -238,9 +237,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -278,7 +277,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -384,7 +383,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -526,7 +525,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -623,7 +622,8 @@
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="110.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="21.88671875" customWidth="1"/>
-    <col min="5" max="6" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="37.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -827,67 +827,67 @@
       <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1">
         <v>1990</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1">
         <v>1991</v>
       </c>
-      <c r="D1" s="2">
+      <c r="D1">
         <v>1992</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E1">
         <v>1993</v>
       </c>
-      <c r="F1" s="2">
+      <c r="F1">
         <v>1994</v>
       </c>
-      <c r="G1" s="2">
+      <c r="G1">
         <v>1995</v>
       </c>
-      <c r="H1" s="2">
+      <c r="H1">
         <v>1996</v>
       </c>
-      <c r="I1" s="2">
+      <c r="I1">
         <v>1997</v>
       </c>
-      <c r="J1" s="2">
+      <c r="J1">
         <v>1998</v>
       </c>
-      <c r="K1" s="2">
+      <c r="K1">
         <v>1999</v>
       </c>
-      <c r="L1" s="2">
+      <c r="L1">
         <v>2000</v>
       </c>
-      <c r="M1" s="2">
+      <c r="M1">
         <v>2001</v>
       </c>
-      <c r="N1" s="2">
+      <c r="N1">
         <v>2002</v>
       </c>
-      <c r="O1" s="2">
+      <c r="O1">
         <v>2003</v>
       </c>
-      <c r="P1" s="2">
+      <c r="P1">
         <v>2004</v>
       </c>
-      <c r="Q1" s="2">
+      <c r="Q1">
         <v>2005</v>
       </c>
-      <c r="R1" s="2">
+      <c r="R1">
         <v>2006</v>
       </c>
-      <c r="S1" s="2">
+      <c r="S1">
         <v>2007</v>
       </c>
-      <c r="T1" s="2">
+      <c r="T1">
         <v>2008</v>
       </c>
-      <c r="U1" s="2">
+      <c r="U1">
         <v>2009</v>
       </c>
-      <c r="V1" s="2">
+      <c r="V1">
         <v>2010</v>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>32966</v>
       </c>
       <c r="C2">
@@ -1233,7 +1233,7 @@
       <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>33334</v>
       </c>
       <c r="C3">
@@ -1257,7 +1257,7 @@
       <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>34069</v>
       </c>
       <c r="C4">
@@ -1281,7 +1281,7 @@
       <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>34802</v>
       </c>
       <c r="C5">
@@ -1305,7 +1305,7 @@
       <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <f>B2+266</f>
         <v>33232</v>
       </c>
@@ -1329,7 +1329,7 @@
       <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <f t="shared" ref="B7:B9" si="1">B3+266</f>
         <v>33600</v>
       </c>
@@ -1353,7 +1353,7 @@
       <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <f t="shared" si="1"/>
         <v>34335</v>
       </c>
@@ -1377,7 +1377,7 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <f t="shared" si="1"/>
         <v>35068</v>
       </c>
@@ -1401,7 +1401,7 @@
       <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>36526</v>
       </c>
       <c r="C10">
@@ -1424,7 +1424,7 @@
       <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>37987</v>
       </c>
       <c r="C11">
